--- a/assets/forms/F14_나이스평가계획업로드작성도우미_작성예시_6학년AI.xlsx
+++ b/assets/forms/F14_나이스평가계획업로드작성도우미_작성예시_6학년AI.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>챗봇 답의 근거 확인과 질문 설계</t>
+          <t>챗봇 답의 근거 확인과 질문 만들기</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
